--- a/artfynd/A 54215-2019 artfynd.xlsx
+++ b/artfynd/A 54215-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54215-2019 artfynd.xlsx
+++ b/artfynd/A 54215-2019 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126918532</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>126919975</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren, Hedda Bring, Lotta Ihse, Eleonor Johansson, Fredrik Wilde, Nicklas Gustavsson, Isac Enetjärn, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
